--- a/MaximusLabs listicle feed.xlsx
+++ b/MaximusLabs listicle feed.xlsx
@@ -6217,11 +6217,11 @@
       <c r="I2" t="str">
         <v>Published by MaximusLabs.ai, which competes with every firm listed. Listed first as publisher; signal rank fourth, printed on our own card. Read the methodology before using the order as a recommendation.</v>
       </c>
-      <c r="J2">
-        <v>46280</v>
-      </c>
-      <c r="K2">
-        <v>46280</v>
+      <c r="J2" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2026-09-15</v>
       </c>
       <c r="L2" t="str">
         <v>Not scraped from other people's rankings. Here is the actual sequence, and what was thrown away at each step.</v>
@@ -6279,11 +6279,11 @@
       <c r="I3" t="str">
         <v>Published by MaximusLabs.ai, which competes with every firm listed. Listed first as publisher; signal rank eighth, printed on our own card. Read the methodology before using the order as a recommendation.</v>
       </c>
-      <c r="J3">
-        <v>46280</v>
-      </c>
-      <c r="K3">
-        <v>46280</v>
+      <c r="J3" t="str">
+        <v>2026-09-15</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2026-09-15</v>
       </c>
       <c r="L3" t="str">
         <v>Built from answer engine capability first, then filtered for B2B SaaS proof. The process separates an agency's general AI-search strength from evidence that it can work in software categories and connect visibility to pipeline, signups, or recurring revenue.</v>

--- a/MaximusLabs listicle feed.xlsx
+++ b/MaximusLabs listicle feed.xlsx
@@ -6239,7 +6239,7 @@
         <v>Compare 10 AEO agencies for cybersecurity by services, pricing, industry evidence, case studies, AI visibility, and limitations.</v>
       </c>
       <c r="Q2" t="str">
-        <v>https://www.maximuslabs.ai/listicles/10-best-aeo-agencies-cybersecurity</v>
+        <v>https://www.maximuslabs.ai/answer-engine-optimizations/cybersecurity-aeo-agencies</v>
       </c>
       <c r="R2" t="str">
         <v>Ratings appear only for platforms each firm is actually on. A live profile with no reviews remains visible.</v>
@@ -6301,7 +6301,7 @@
         <v>Compare 10 AEO agencies for B2B SaaS by services, pricing, client evidence, case studies, AI visibility, and limitations.</v>
       </c>
       <c r="Q3" t="str">
-        <v>https://www.maximuslabs.ai/listicles/10-best-aeo-agencies-b2b-saas</v>
+        <v>https://www.maximuslabs.ai/answer-engine-optimizations/b2b-saas-aeo-geo-agencies</v>
       </c>
       <c r="R3" t="str">
         <v>Ratings appear only for platforms each firm is actually on. A live profile with no reviews remains visible.</v>
